--- a/population-projection/src/main/resources/population_data/RSFSR/RSFSR-population-ADH.xlsx
+++ b/population-projection/src/main/resources/population_data/RSFSR/RSFSR-population-ADH.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-time-progression\src\main\resources\population_data\RSFSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\population-projection\src\main\resources\population_data\RSFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E15D4D-83DA-4950-A620-9DC1BDF2B5A8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC9F169-68A3-4B84-BFFD-0343E4190E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{74EFCB51-A7FA-461C-9490-A2B1101B0974}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{74EFCB51-A7FA-461C-9490-A2B1101B0974}"/>
   </bookViews>
   <sheets>
     <sheet name="Comment" sheetId="1" r:id="rId1"/>
     <sheet name="Males" sheetId="2" r:id="rId2"/>
     <sheet name="Females" sheetId="3" r:id="rId3"/>
+    <sheet name="Both" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
   <si>
     <t>возраст</t>
   </si>
@@ -106,6 +112,12 @@
   <si>
     <t>На начало указанного года.</t>
   </si>
+  <si>
+    <t>Страница Both выичисленп по Males и Females.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">проверка </t>
+  </si>
 </sst>
 </file>
 
@@ -148,11 +160,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -173,9 +188,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -213,7 +228,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -319,7 +334,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -461,7 +476,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -469,22 +484,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91E475B6-F783-4F96-9497-603C30DA3C90}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -495,9 +515,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4811567-333B-4FE3-A82C-C293FD174F3B}">
   <dimension ref="A1:AD22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +609,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -681,7 +701,7 @@
         <v>52465</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -773,7 +793,7 @@
         <v>6878</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -865,7 +885,7 @@
         <v>6367</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -957,7 +977,7 @@
         <v>4220</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,7 +1069,7 @@
         <v>4540</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,7 +1161,7 @@
         <v>5775</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1233,7 +1253,7 @@
         <v>5249</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1325,7 +1345,7 @@
         <v>4947</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1417,7 +1437,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1509,7 +1529,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1601,7 +1621,7 @@
         <v>2687</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1693,7 +1713,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1785,7 +1805,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1877,7 +1897,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1969,7 +1989,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -2061,7 +2081,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2153,7 +2173,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -2245,7 +2265,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -2337,7 +2357,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2369,7 +2389,7 @@
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -2499,12 +2519,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F52DEE-6184-469A-BE3D-559649851B44}">
   <dimension ref="A1:AD22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.15625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2596,7 +2616,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2688,7 +2708,7 @@
         <v>65151</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2780,7 +2800,7 @@
         <v>6621</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2872,7 +2892,7 @@
         <v>6166</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2964,7 +2984,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -3056,7 +3076,7 @@
         <v>4511</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -3148,7 +3168,7 @@
         <v>5740</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -3240,7 +3260,7 @@
         <v>5358</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -3332,7 +3352,7 @@
         <v>5941</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -3424,7 +3444,7 @@
         <v>4049</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -3516,7 +3536,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -3608,7 +3628,7 @@
         <v>4514</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -3700,7 +3720,7 @@
         <v>3798</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -3792,7 +3812,7 @@
         <v>3279</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -3884,7 +3904,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -3976,7 +3996,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -4068,7 +4088,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -4160,7 +4180,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -4252,7 +4272,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -4344,7 +4364,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4376,7 +4396,7 @@
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -4500,4 +4520,2581 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05D6201-6078-4E81-ACE9-43893023B1AE}">
+  <dimension ref="A1:AD22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="str">
+        <f>Males!A1</f>
+        <v>возраст</v>
+      </c>
+      <c r="B1" s="4">
+        <f>Males!B1</f>
+        <v>1927</v>
+      </c>
+      <c r="C1" s="4">
+        <f>Males!C1</f>
+        <v>1928</v>
+      </c>
+      <c r="D1" s="4">
+        <f>Males!D1</f>
+        <v>1929</v>
+      </c>
+      <c r="E1" s="4">
+        <f>Males!E1</f>
+        <v>1930</v>
+      </c>
+      <c r="F1" s="4">
+        <f>Males!F1</f>
+        <v>1931</v>
+      </c>
+      <c r="G1" s="4">
+        <f>Males!G1</f>
+        <v>1932</v>
+      </c>
+      <c r="H1" s="4">
+        <f>Males!H1</f>
+        <v>1933</v>
+      </c>
+      <c r="I1" s="4">
+        <f>Males!I1</f>
+        <v>1934</v>
+      </c>
+      <c r="J1" s="4">
+        <f>Males!J1</f>
+        <v>1935</v>
+      </c>
+      <c r="K1" s="4">
+        <f>Males!K1</f>
+        <v>1936</v>
+      </c>
+      <c r="L1" s="4">
+        <f>Males!L1</f>
+        <v>1937</v>
+      </c>
+      <c r="M1" s="4">
+        <f>Males!M1</f>
+        <v>1938</v>
+      </c>
+      <c r="N1" s="4">
+        <f>Males!N1</f>
+        <v>1939</v>
+      </c>
+      <c r="O1" s="4">
+        <f>Males!O1</f>
+        <v>1940</v>
+      </c>
+      <c r="P1" s="4">
+        <f>Males!P1</f>
+        <v>1941</v>
+      </c>
+      <c r="Q1" s="4">
+        <f>Males!Q1</f>
+        <v>1946</v>
+      </c>
+      <c r="R1" s="4">
+        <f>Males!R1</f>
+        <v>1947</v>
+      </c>
+      <c r="S1" s="4">
+        <f>Males!S1</f>
+        <v>1948</v>
+      </c>
+      <c r="T1" s="4">
+        <f>Males!T1</f>
+        <v>1949</v>
+      </c>
+      <c r="U1" s="4">
+        <f>Males!U1</f>
+        <v>1950</v>
+      </c>
+      <c r="V1" s="4">
+        <f>Males!V1</f>
+        <v>1951</v>
+      </c>
+      <c r="W1" s="4">
+        <f>Males!W1</f>
+        <v>1952</v>
+      </c>
+      <c r="X1" s="4">
+        <f>Males!X1</f>
+        <v>1953</v>
+      </c>
+      <c r="Y1" s="4">
+        <f>Males!Y1</f>
+        <v>1954</v>
+      </c>
+      <c r="Z1" s="4">
+        <f>Males!Z1</f>
+        <v>1955</v>
+      </c>
+      <c r="AA1" s="4">
+        <f>Males!AA1</f>
+        <v>1956</v>
+      </c>
+      <c r="AB1" s="4">
+        <f>Males!AB1</f>
+        <v>1957</v>
+      </c>
+      <c r="AC1" s="4">
+        <f>Males!AC1</f>
+        <v>1958</v>
+      </c>
+      <c r="AD1" s="4">
+        <f>Males!AD1</f>
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="str">
+        <f>Males!A2</f>
+        <v>всего</v>
+      </c>
+      <c r="B2" s="2">
+        <f>Males!B2+Females!B2</f>
+        <v>93604</v>
+      </c>
+      <c r="C2" s="2">
+        <f>Males!C2+Females!C2</f>
+        <v>95587</v>
+      </c>
+      <c r="D2" s="2">
+        <f>Males!D2+Females!D2</f>
+        <v>97721</v>
+      </c>
+      <c r="E2" s="2">
+        <f>Males!E2+Females!E2</f>
+        <v>99566</v>
+      </c>
+      <c r="F2" s="2">
+        <f>Males!F2+Females!F2</f>
+        <v>101272</v>
+      </c>
+      <c r="G2" s="2">
+        <f>Males!G2+Females!G2</f>
+        <v>102625</v>
+      </c>
+      <c r="H2" s="2">
+        <f>Males!H2+Females!H2</f>
+        <v>103648</v>
+      </c>
+      <c r="I2" s="2">
+        <f>Males!I2+Females!I2</f>
+        <v>101763</v>
+      </c>
+      <c r="J2" s="2">
+        <f>Males!J2+Females!J2</f>
+        <v>102080</v>
+      </c>
+      <c r="K2" s="2">
+        <f>Males!K2+Females!K2</f>
+        <v>103288</v>
+      </c>
+      <c r="L2" s="2">
+        <f>Males!L2+Females!L2</f>
+        <v>104520</v>
+      </c>
+      <c r="M2" s="2">
+        <f>Males!M2+Females!M2</f>
+        <v>106195</v>
+      </c>
+      <c r="N2" s="2">
+        <f>Males!N2+Females!N2</f>
+        <v>107893</v>
+      </c>
+      <c r="O2" s="2">
+        <f>Males!O2+Females!O2</f>
+        <v>109678</v>
+      </c>
+      <c r="P2" s="2">
+        <f>Males!P2+Females!P2</f>
+        <v>110988</v>
+      </c>
+      <c r="Q2" s="2">
+        <f>Males!Q2+Females!Q2</f>
+        <v>97548</v>
+      </c>
+      <c r="R2" s="2">
+        <f>Males!R2+Females!R2</f>
+        <v>98509</v>
+      </c>
+      <c r="S2" s="2">
+        <f>Males!S2+Females!S2</f>
+        <v>99159</v>
+      </c>
+      <c r="T2" s="2">
+        <f>Males!T2+Females!T2</f>
+        <v>100252</v>
+      </c>
+      <c r="U2" s="2">
+        <f>Males!U2+Females!U2</f>
+        <v>102067</v>
+      </c>
+      <c r="V2" s="2">
+        <f>Males!V2+Females!V2</f>
+        <v>103599</v>
+      </c>
+      <c r="W2" s="2">
+        <f>Males!W2+Females!W2</f>
+        <v>105278</v>
+      </c>
+      <c r="X2" s="2">
+        <f>Males!X2+Females!X2</f>
+        <v>107049</v>
+      </c>
+      <c r="Y2" s="2">
+        <f>Males!Y2+Females!Y2</f>
+        <v>108607</v>
+      </c>
+      <c r="Z2" s="2">
+        <f>Males!Z2+Females!Z2</f>
+        <v>110678</v>
+      </c>
+      <c r="AA2" s="2">
+        <f>Males!AA2+Females!AA2</f>
+        <v>112465</v>
+      </c>
+      <c r="AB2" s="2">
+        <f>Males!AB2+Females!AB2</f>
+        <v>114189</v>
+      </c>
+      <c r="AC2" s="2">
+        <f>Males!AC2+Females!AC2</f>
+        <v>115881</v>
+      </c>
+      <c r="AD2" s="2">
+        <f>Males!AD2+Females!AD2</f>
+        <v>117616</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="str">
+        <f>Males!A3</f>
+        <v>0-4</v>
+      </c>
+      <c r="B3" s="2">
+        <f>Males!B3+Females!B3</f>
+        <v>14880</v>
+      </c>
+      <c r="C3" s="2">
+        <f>Males!C3+Females!C3</f>
+        <v>15658</v>
+      </c>
+      <c r="D3" s="2">
+        <f>Males!D3+Females!D3</f>
+        <v>16227</v>
+      </c>
+      <c r="E3" s="2">
+        <f>Males!E3+Females!E3</f>
+        <v>16420</v>
+      </c>
+      <c r="F3" s="2">
+        <f>Males!F3+Females!F3</f>
+        <v>16248</v>
+      </c>
+      <c r="G3" s="2">
+        <f>Males!G3+Females!G3</f>
+        <v>15892</v>
+      </c>
+      <c r="H3" s="2">
+        <f>Males!H3+Females!H3</f>
+        <v>15239</v>
+      </c>
+      <c r="I3" s="2">
+        <f>Males!I3+Females!I3</f>
+        <v>13550</v>
+      </c>
+      <c r="J3" s="2">
+        <f>Males!J3+Females!J3</f>
+        <v>12389</v>
+      </c>
+      <c r="K3" s="2">
+        <f>Males!K3+Females!K3</f>
+        <v>12139</v>
+      </c>
+      <c r="L3" s="2">
+        <f>Males!L3+Females!L3</f>
+        <v>11990</v>
+      </c>
+      <c r="M3" s="2">
+        <f>Males!M3+Females!M3</f>
+        <v>12668</v>
+      </c>
+      <c r="N3" s="2">
+        <f>Males!N3+Females!N3</f>
+        <v>13689</v>
+      </c>
+      <c r="O3" s="2">
+        <f>Males!O3+Females!O3</f>
+        <v>14730</v>
+      </c>
+      <c r="P3" s="2">
+        <f>Males!P3+Females!P3</f>
+        <v>14848</v>
+      </c>
+      <c r="Q3" s="2">
+        <f>Males!Q3+Females!Q3</f>
+        <v>6825</v>
+      </c>
+      <c r="R3" s="2">
+        <f>Males!R3+Females!R3</f>
+        <v>6848</v>
+      </c>
+      <c r="S3" s="2">
+        <f>Males!S3+Females!S3</f>
+        <v>7642</v>
+      </c>
+      <c r="T3" s="2">
+        <f>Males!T3+Females!T3</f>
+        <v>8812</v>
+      </c>
+      <c r="U3" s="2">
+        <f>Males!U3+Females!U3</f>
+        <v>10513</v>
+      </c>
+      <c r="V3" s="2">
+        <f>Males!V3+Females!V3</f>
+        <v>11703</v>
+      </c>
+      <c r="W3" s="2">
+        <f>Males!W3+Females!W3</f>
+        <v>12117</v>
+      </c>
+      <c r="X3" s="2">
+        <f>Males!X3+Females!X3</f>
+        <v>12490</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>Males!Y3+Females!Y3</f>
+        <v>12873</v>
+      </c>
+      <c r="Z3" s="2">
+        <f>Males!Z3+Females!Z3</f>
+        <v>12941</v>
+      </c>
+      <c r="AA3" s="2">
+        <f>Males!AA3+Females!AA3</f>
+        <v>13156</v>
+      </c>
+      <c r="AB3" s="2">
+        <f>Males!AB3+Females!AB3</f>
+        <v>13219</v>
+      </c>
+      <c r="AC3" s="2">
+        <f>Males!AC3+Females!AC3</f>
+        <v>13311</v>
+      </c>
+      <c r="AD3" s="2">
+        <f>Males!AD3+Females!AD3</f>
+        <v>13499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="str">
+        <f>Males!A4</f>
+        <v>5-9</v>
+      </c>
+      <c r="B4" s="2">
+        <f>Males!B4+Females!B4</f>
+        <v>9519</v>
+      </c>
+      <c r="C4" s="2">
+        <f>Males!C4+Females!C4</f>
+        <v>9967</v>
+      </c>
+      <c r="D4" s="2">
+        <f>Males!D4+Females!D4</f>
+        <v>10437</v>
+      </c>
+      <c r="E4" s="2">
+        <f>Males!E4+Females!E4</f>
+        <v>11156</v>
+      </c>
+      <c r="F4" s="2">
+        <f>Males!F4+Females!F4</f>
+        <v>12060</v>
+      </c>
+      <c r="G4" s="2">
+        <f>Males!G4+Females!G4</f>
+        <v>12978</v>
+      </c>
+      <c r="H4" s="2">
+        <f>Males!H4+Females!H4</f>
+        <v>13759</v>
+      </c>
+      <c r="I4" s="2">
+        <f>Males!I4+Females!I4</f>
+        <v>13934</v>
+      </c>
+      <c r="J4" s="2">
+        <f>Males!J4+Females!J4</f>
+        <v>14033</v>
+      </c>
+      <c r="K4" s="2">
+        <f>Males!K4+Females!K4</f>
+        <v>13745</v>
+      </c>
+      <c r="L4" s="2">
+        <f>Males!L4+Females!L4</f>
+        <v>13273</v>
+      </c>
+      <c r="M4" s="2">
+        <f>Males!M4+Females!M4</f>
+        <v>12575</v>
+      </c>
+      <c r="N4" s="2">
+        <f>Males!N4+Females!N4</f>
+        <v>11656</v>
+      </c>
+      <c r="O4" s="2">
+        <f>Males!O4+Females!O4</f>
+        <v>10800</v>
+      </c>
+      <c r="P4" s="2">
+        <f>Males!P4+Females!P4</f>
+        <v>10487</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>Males!Q4+Females!Q4</f>
+        <v>12972</v>
+      </c>
+      <c r="R4" s="2">
+        <f>Males!R4+Females!R4</f>
+        <v>12632</v>
+      </c>
+      <c r="S4" s="2">
+        <f>Males!S4+Females!S4</f>
+        <v>11170</v>
+      </c>
+      <c r="T4" s="2">
+        <f>Males!T4+Females!T4</f>
+        <v>9172</v>
+      </c>
+      <c r="U4" s="2">
+        <f>Males!U4+Females!U4</f>
+        <v>7498</v>
+      </c>
+      <c r="V4" s="2">
+        <f>Males!V4+Females!V4</f>
+        <v>6362</v>
+      </c>
+      <c r="W4" s="2">
+        <f>Males!W4+Females!W4</f>
+        <v>6283</v>
+      </c>
+      <c r="X4" s="2">
+        <f>Males!X4+Females!X4</f>
+        <v>7165</v>
+      </c>
+      <c r="Y4" s="2">
+        <f>Males!Y4+Females!Y4</f>
+        <v>8377</v>
+      </c>
+      <c r="Z4" s="2">
+        <f>Males!Z4+Females!Z4</f>
+        <v>10065</v>
+      </c>
+      <c r="AA4" s="2">
+        <f>Males!AA4+Females!AA4</f>
+        <v>11257</v>
+      </c>
+      <c r="AB4" s="2">
+        <f>Males!AB4+Females!AB4</f>
+        <v>11733</v>
+      </c>
+      <c r="AC4" s="2">
+        <f>Males!AC4+Females!AC4</f>
+        <v>12129</v>
+      </c>
+      <c r="AD4" s="2">
+        <f>Males!AD4+Females!AD4</f>
+        <v>12533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="str">
+        <f>Males!A5</f>
+        <v>10-14</v>
+      </c>
+      <c r="B5" s="2">
+        <f>Males!B5+Females!B5</f>
+        <v>11007</v>
+      </c>
+      <c r="C5" s="2">
+        <f>Males!C5+Females!C5</f>
+        <v>10269</v>
+      </c>
+      <c r="D5" s="2">
+        <f>Males!D5+Females!D5</f>
+        <v>9733</v>
+      </c>
+      <c r="E5" s="2">
+        <f>Males!E5+Females!E5</f>
+        <v>9140</v>
+      </c>
+      <c r="F5" s="2">
+        <f>Males!F5+Females!F5</f>
+        <v>8958</v>
+      </c>
+      <c r="G5" s="2">
+        <f>Males!G5+Females!G5</f>
+        <v>9155</v>
+      </c>
+      <c r="H5" s="2">
+        <f>Males!H5+Females!H5</f>
+        <v>9591</v>
+      </c>
+      <c r="I5" s="2">
+        <f>Males!I5+Females!I5</f>
+        <v>9868</v>
+      </c>
+      <c r="J5" s="2">
+        <f>Males!J5+Females!J5</f>
+        <v>10601</v>
+      </c>
+      <c r="K5" s="2">
+        <f>Males!K5+Females!K5</f>
+        <v>11553</v>
+      </c>
+      <c r="L5" s="2">
+        <f>Males!L5+Females!L5</f>
+        <v>12543</v>
+      </c>
+      <c r="M5" s="2">
+        <f>Males!M5+Females!M5</f>
+        <v>13314</v>
+      </c>
+      <c r="N5" s="2">
+        <f>Males!N5+Females!N5</f>
+        <v>13738</v>
+      </c>
+      <c r="O5" s="2">
+        <f>Males!O5+Females!O5</f>
+        <v>13771</v>
+      </c>
+      <c r="P5" s="2">
+        <f>Males!P5+Females!P5</f>
+        <v>13450</v>
+      </c>
+      <c r="Q5" s="2">
+        <f>Males!Q5+Females!Q5</f>
+        <v>10059</v>
+      </c>
+      <c r="R5" s="2">
+        <f>Males!R5+Females!R5</f>
+        <v>10319</v>
+      </c>
+      <c r="S5" s="2">
+        <f>Males!S5+Females!S5</f>
+        <v>10821</v>
+      </c>
+      <c r="T5" s="2">
+        <f>Males!T5+Females!T5</f>
+        <v>11790</v>
+      </c>
+      <c r="U5" s="2">
+        <f>Males!U5+Females!U5</f>
+        <v>12559</v>
+      </c>
+      <c r="V5" s="2">
+        <f>Males!V5+Females!V5</f>
+        <v>12768</v>
+      </c>
+      <c r="W5" s="2">
+        <f>Males!W5+Females!W5</f>
+        <v>12461</v>
+      </c>
+      <c r="X5" s="2">
+        <f>Males!X5+Females!X5</f>
+        <v>11054</v>
+      </c>
+      <c r="Y5" s="2">
+        <f>Males!Y5+Females!Y5</f>
+        <v>9087</v>
+      </c>
+      <c r="Z5" s="2">
+        <f>Males!Z5+Females!Z5</f>
+        <v>7435</v>
+      </c>
+      <c r="AA5" s="2">
+        <f>Males!AA5+Females!AA5</f>
+        <v>6309</v>
+      </c>
+      <c r="AB5" s="2">
+        <f>Males!AB5+Females!AB5</f>
+        <v>6230</v>
+      </c>
+      <c r="AC5" s="2">
+        <f>Males!AC5+Females!AC5</f>
+        <v>7109</v>
+      </c>
+      <c r="AD5" s="2">
+        <f>Males!AD5+Females!AD5</f>
+        <v>8320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="str">
+        <f>Males!A6</f>
+        <v>15-19</v>
+      </c>
+      <c r="B6" s="2">
+        <f>Males!B6+Females!B6</f>
+        <v>10881</v>
+      </c>
+      <c r="C6" s="2">
+        <f>Males!C6+Females!C6</f>
+        <v>11219</v>
+      </c>
+      <c r="D6" s="2">
+        <f>Males!D6+Females!D6</f>
+        <v>11501</v>
+      </c>
+      <c r="E6" s="2">
+        <f>Males!E6+Females!E6</f>
+        <v>11689</v>
+      </c>
+      <c r="F6" s="2">
+        <f>Males!F6+Females!F6</f>
+        <v>11412</v>
+      </c>
+      <c r="G6" s="2">
+        <f>Males!G6+Females!G6</f>
+        <v>10772</v>
+      </c>
+      <c r="H6" s="2">
+        <f>Males!H6+Females!H6</f>
+        <v>10034</v>
+      </c>
+      <c r="I6" s="2">
+        <f>Males!I6+Females!I6</f>
+        <v>9302</v>
+      </c>
+      <c r="J6" s="2">
+        <f>Males!J6+Females!J6</f>
+        <v>8695</v>
+      </c>
+      <c r="K6" s="2">
+        <f>Males!K6+Females!K6</f>
+        <v>8492</v>
+      </c>
+      <c r="L6" s="2">
+        <f>Males!L6+Females!L6</f>
+        <v>8663</v>
+      </c>
+      <c r="M6" s="2">
+        <f>Males!M6+Females!M6</f>
+        <v>9107</v>
+      </c>
+      <c r="N6" s="2">
+        <f>Males!N6+Females!N6</f>
+        <v>9608</v>
+      </c>
+      <c r="O6" s="2">
+        <f>Males!O6+Females!O6</f>
+        <v>10410</v>
+      </c>
+      <c r="P6" s="2">
+        <f>Males!P6+Females!P6</f>
+        <v>11410</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>Males!Q6+Females!Q6</f>
+        <v>12716</v>
+      </c>
+      <c r="R6" s="2">
+        <f>Males!R6+Females!R6</f>
+        <v>12348</v>
+      </c>
+      <c r="S6" s="2">
+        <f>Males!S6+Females!S6</f>
+        <v>11880</v>
+      </c>
+      <c r="T6" s="2">
+        <f>Males!T6+Females!T6</f>
+        <v>11090</v>
+      </c>
+      <c r="U6" s="2">
+        <f>Males!U6+Females!U6</f>
+        <v>10324</v>
+      </c>
+      <c r="V6" s="2">
+        <f>Males!V6+Females!V6</f>
+        <v>9989</v>
+      </c>
+      <c r="W6" s="2">
+        <f>Males!W6+Females!W6</f>
+        <v>10266</v>
+      </c>
+      <c r="X6" s="2">
+        <f>Males!X6+Females!X6</f>
+        <v>10799</v>
+      </c>
+      <c r="Y6" s="2">
+        <f>Males!Y6+Females!Y6</f>
+        <v>11760</v>
+      </c>
+      <c r="Z6" s="2">
+        <f>Males!Z6+Females!Z6</f>
+        <v>12573</v>
+      </c>
+      <c r="AA6" s="2">
+        <f>Males!AA6+Females!AA6</f>
+        <v>12767</v>
+      </c>
+      <c r="AB6" s="2">
+        <f>Males!AB6+Females!AB6</f>
+        <v>12446</v>
+      </c>
+      <c r="AC6" s="2">
+        <f>Males!AC6+Females!AC6</f>
+        <v>11026</v>
+      </c>
+      <c r="AD6" s="2">
+        <f>Males!AD6+Females!AD6</f>
+        <v>9051</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="str">
+        <f>Males!A7</f>
+        <v>20-24</v>
+      </c>
+      <c r="B7" s="2">
+        <f>Males!B7+Females!B7</f>
+        <v>8889</v>
+      </c>
+      <c r="C7" s="2">
+        <f>Males!C7+Females!C7</f>
+        <v>9192</v>
+      </c>
+      <c r="D7" s="2">
+        <f>Males!D7+Females!D7</f>
+        <v>9533</v>
+      </c>
+      <c r="E7" s="2">
+        <f>Males!E7+Females!E7</f>
+        <v>9886</v>
+      </c>
+      <c r="F7" s="2">
+        <f>Males!F7+Females!F7</f>
+        <v>10239</v>
+      </c>
+      <c r="G7" s="2">
+        <f>Males!G7+Females!G7</f>
+        <v>10554</v>
+      </c>
+      <c r="H7" s="2">
+        <f>Males!H7+Females!H7</f>
+        <v>10845</v>
+      </c>
+      <c r="I7" s="2">
+        <f>Males!I7+Females!I7</f>
+        <v>10863</v>
+      </c>
+      <c r="J7" s="2">
+        <f>Males!J7+Females!J7</f>
+        <v>11030</v>
+      </c>
+      <c r="K7" s="2">
+        <f>Males!K7+Females!K7</f>
+        <v>10787</v>
+      </c>
+      <c r="L7" s="2">
+        <f>Males!L7+Females!L7</f>
+        <v>10220</v>
+      </c>
+      <c r="M7" s="2">
+        <f>Males!M7+Females!M7</f>
+        <v>9531</v>
+      </c>
+      <c r="N7" s="2">
+        <f>Males!N7+Females!N7</f>
+        <v>9003</v>
+      </c>
+      <c r="O7" s="2">
+        <f>Males!O7+Females!O7</f>
+        <v>8431</v>
+      </c>
+      <c r="P7" s="2">
+        <f>Males!P7+Females!P7</f>
+        <v>8247</v>
+      </c>
+      <c r="Q7" s="2">
+        <f>Males!Q7+Females!Q7</f>
+        <v>8842</v>
+      </c>
+      <c r="R7" s="2">
+        <f>Males!R7+Females!R7</f>
+        <v>9763</v>
+      </c>
+      <c r="S7" s="2">
+        <f>Males!S7+Females!S7</f>
+        <v>10674</v>
+      </c>
+      <c r="T7" s="2">
+        <f>Males!T7+Females!T7</f>
+        <v>11492</v>
+      </c>
+      <c r="U7" s="2">
+        <f>Males!U7+Females!U7</f>
+        <v>12047</v>
+      </c>
+      <c r="V7" s="2">
+        <f>Males!V7+Females!V7</f>
+        <v>12253</v>
+      </c>
+      <c r="W7" s="2">
+        <f>Males!W7+Females!W7</f>
+        <v>11993</v>
+      </c>
+      <c r="X7" s="2">
+        <f>Males!X7+Females!X7</f>
+        <v>11622</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>Males!Y7+Females!Y7</f>
+        <v>10835</v>
+      </c>
+      <c r="Z7" s="2">
+        <f>Males!Z7+Females!Z7</f>
+        <v>10138</v>
+      </c>
+      <c r="AA7" s="2">
+        <f>Males!AA7+Females!AA7</f>
+        <v>9830</v>
+      </c>
+      <c r="AB7" s="2">
+        <f>Males!AB7+Females!AB7</f>
+        <v>10097</v>
+      </c>
+      <c r="AC7" s="2">
+        <f>Males!AC7+Females!AC7</f>
+        <v>10584</v>
+      </c>
+      <c r="AD7" s="2">
+        <f>Males!AD7+Females!AD7</f>
+        <v>11515</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="str">
+        <f>Males!A8</f>
+        <v>25-29</v>
+      </c>
+      <c r="B8" s="2">
+        <f>Males!B8+Females!B8</f>
+        <v>7329</v>
+      </c>
+      <c r="C8" s="2">
+        <f>Males!C8+Females!C8</f>
+        <v>7584</v>
+      </c>
+      <c r="D8" s="2">
+        <f>Males!D8+Females!D8</f>
+        <v>7829</v>
+      </c>
+      <c r="E8" s="2">
+        <f>Males!E8+Females!E8</f>
+        <v>8074</v>
+      </c>
+      <c r="F8" s="2">
+        <f>Males!F8+Females!F8</f>
+        <v>8337</v>
+      </c>
+      <c r="G8" s="2">
+        <f>Males!G8+Females!G8</f>
+        <v>8603</v>
+      </c>
+      <c r="H8" s="2">
+        <f>Males!H8+Females!H8</f>
+        <v>8890</v>
+      </c>
+      <c r="I8" s="2">
+        <f>Males!I8+Females!I8</f>
+        <v>9006</v>
+      </c>
+      <c r="J8" s="2">
+        <f>Males!J8+Females!J8</f>
+        <v>9304</v>
+      </c>
+      <c r="K8" s="2">
+        <f>Males!K8+Females!K8</f>
+        <v>9614</v>
+      </c>
+      <c r="L8" s="2">
+        <f>Males!L8+Females!L8</f>
+        <v>9906</v>
+      </c>
+      <c r="M8" s="2">
+        <f>Males!M8+Females!M8</f>
+        <v>10176</v>
+      </c>
+      <c r="N8" s="2">
+        <f>Males!N8+Females!N8</f>
+        <v>10410</v>
+      </c>
+      <c r="O8" s="2">
+        <f>Males!O8+Females!O8</f>
+        <v>10655</v>
+      </c>
+      <c r="P8" s="2">
+        <f>Males!P8+Females!P8</f>
+        <v>10485</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>Males!Q8+Females!Q8</f>
+        <v>6261</v>
+      </c>
+      <c r="R8" s="2">
+        <f>Males!R8+Females!R8</f>
+        <v>6323</v>
+      </c>
+      <c r="S8" s="2">
+        <f>Males!S8+Females!S8</f>
+        <v>6552</v>
+      </c>
+      <c r="T8" s="2">
+        <f>Males!T8+Females!T8</f>
+        <v>6977</v>
+      </c>
+      <c r="U8" s="2">
+        <f>Males!U8+Females!U8</f>
+        <v>7601</v>
+      </c>
+      <c r="V8" s="2">
+        <f>Males!V8+Females!V8</f>
+        <v>8424</v>
+      </c>
+      <c r="W8" s="2">
+        <f>Males!W8+Females!W8</f>
+        <v>9383</v>
+      </c>
+      <c r="X8" s="2">
+        <f>Males!X8+Females!X8</f>
+        <v>10340</v>
+      </c>
+      <c r="Y8" s="2">
+        <f>Males!Y8+Females!Y8</f>
+        <v>11142</v>
+      </c>
+      <c r="Z8" s="2">
+        <f>Males!Z8+Females!Z8</f>
+        <v>11760</v>
+      </c>
+      <c r="AA8" s="2">
+        <f>Males!AA8+Females!AA8</f>
+        <v>11997</v>
+      </c>
+      <c r="AB8" s="2">
+        <f>Males!AB8+Females!AB8</f>
+        <v>11750</v>
+      </c>
+      <c r="AC8" s="2">
+        <f>Males!AC8+Females!AC8</f>
+        <v>11373</v>
+      </c>
+      <c r="AD8" s="2">
+        <f>Males!AD8+Females!AD8</f>
+        <v>10607</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="str">
+        <f>Males!A9</f>
+        <v>30-34</v>
+      </c>
+      <c r="B9" s="2">
+        <f>Males!B9+Females!B9</f>
+        <v>5618</v>
+      </c>
+      <c r="C9" s="2">
+        <f>Males!C9+Females!C9</f>
+        <v>5845</v>
+      </c>
+      <c r="D9" s="2">
+        <f>Males!D9+Females!D9</f>
+        <v>6134</v>
+      </c>
+      <c r="E9" s="2">
+        <f>Males!E9+Females!E9</f>
+        <v>6441</v>
+      </c>
+      <c r="F9" s="2">
+        <f>Males!F9+Females!F9</f>
+        <v>6750</v>
+      </c>
+      <c r="G9" s="2">
+        <f>Males!G9+Females!G9</f>
+        <v>7026</v>
+      </c>
+      <c r="H9" s="2">
+        <f>Males!H9+Females!H9</f>
+        <v>7280</v>
+      </c>
+      <c r="I9" s="2">
+        <f>Males!I9+Females!I9</f>
+        <v>7374</v>
+      </c>
+      <c r="J9" s="2">
+        <f>Males!J9+Females!J9</f>
+        <v>7623</v>
+      </c>
+      <c r="K9" s="2">
+        <f>Males!K9+Females!K9</f>
+        <v>7898</v>
+      </c>
+      <c r="L9" s="2">
+        <f>Males!L9+Females!L9</f>
+        <v>8180</v>
+      </c>
+      <c r="M9" s="2">
+        <f>Males!M9+Females!M9</f>
+        <v>8457</v>
+      </c>
+      <c r="N9" s="2">
+        <f>Males!N9+Females!N9</f>
+        <v>8727</v>
+      </c>
+      <c r="O9" s="2">
+        <f>Males!O9+Females!O9</f>
+        <v>9001</v>
+      </c>
+      <c r="P9" s="2">
+        <f>Males!P9+Females!P9</f>
+        <v>9291</v>
+      </c>
+      <c r="Q9" s="2">
+        <f>Males!Q9+Females!Q9</f>
+        <v>7792</v>
+      </c>
+      <c r="R9" s="2">
+        <f>Males!R9+Females!R9</f>
+        <v>7371</v>
+      </c>
+      <c r="S9" s="2">
+        <f>Males!S9+Females!S9</f>
+        <v>6871</v>
+      </c>
+      <c r="T9" s="2">
+        <f>Males!T9+Females!T9</f>
+        <v>6458</v>
+      </c>
+      <c r="U9" s="2">
+        <f>Males!U9+Females!U9</f>
+        <v>6147</v>
+      </c>
+      <c r="V9" s="2">
+        <f>Males!V9+Females!V9</f>
+        <v>5995</v>
+      </c>
+      <c r="W9" s="2">
+        <f>Males!W9+Females!W9</f>
+        <v>6078</v>
+      </c>
+      <c r="X9" s="2">
+        <f>Males!X9+Females!X9</f>
+        <v>6357</v>
+      </c>
+      <c r="Y9" s="2">
+        <f>Males!Y9+Females!Y9</f>
+        <v>6776</v>
+      </c>
+      <c r="Z9" s="2">
+        <f>Males!Z9+Females!Z9</f>
+        <v>7413</v>
+      </c>
+      <c r="AA9" s="2">
+        <f>Males!AA9+Females!AA9</f>
+        <v>8229</v>
+      </c>
+      <c r="AB9" s="2">
+        <f>Males!AB9+Females!AB9</f>
+        <v>9167</v>
+      </c>
+      <c r="AC9" s="2">
+        <f>Males!AC9+Females!AC9</f>
+        <v>10094</v>
+      </c>
+      <c r="AD9" s="2">
+        <f>Males!AD9+Females!AD9</f>
+        <v>10888</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="str">
+        <f>Males!A10</f>
+        <v>35-39</v>
+      </c>
+      <c r="B10" s="2">
+        <f>Males!B10+Females!B10</f>
+        <v>5091</v>
+      </c>
+      <c r="C10" s="2">
+        <f>Males!C10+Females!C10</f>
+        <v>5082</v>
+      </c>
+      <c r="D10" s="2">
+        <f>Males!D10+Females!D10</f>
+        <v>5083</v>
+      </c>
+      <c r="E10" s="2">
+        <f>Males!E10+Females!E10</f>
+        <v>5110</v>
+      </c>
+      <c r="F10" s="2">
+        <f>Males!F10+Females!F10</f>
+        <v>5206</v>
+      </c>
+      <c r="G10" s="2">
+        <f>Males!G10+Females!G10</f>
+        <v>5360</v>
+      </c>
+      <c r="H10" s="2">
+        <f>Males!H10+Females!H10</f>
+        <v>5574</v>
+      </c>
+      <c r="I10" s="2">
+        <f>Males!I10+Females!I10</f>
+        <v>5712</v>
+      </c>
+      <c r="J10" s="2">
+        <f>Males!J10+Females!J10</f>
+        <v>5988</v>
+      </c>
+      <c r="K10" s="2">
+        <f>Males!K10+Females!K10</f>
+        <v>6278</v>
+      </c>
+      <c r="L10" s="2">
+        <f>Males!L10+Females!L10</f>
+        <v>6563</v>
+      </c>
+      <c r="M10" s="2">
+        <f>Males!M10+Females!M10</f>
+        <v>6839</v>
+      </c>
+      <c r="N10" s="2">
+        <f>Males!N10+Females!N10</f>
+        <v>7115</v>
+      </c>
+      <c r="O10" s="2">
+        <f>Males!O10+Females!O10</f>
+        <v>7384</v>
+      </c>
+      <c r="P10" s="2">
+        <f>Males!P10+Females!P10</f>
+        <v>7652</v>
+      </c>
+      <c r="Q10" s="2">
+        <f>Males!Q10+Females!Q10</f>
+        <v>7159</v>
+      </c>
+      <c r="R10" s="2">
+        <f>Males!R10+Females!R10</f>
+        <v>7349</v>
+      </c>
+      <c r="S10" s="2">
+        <f>Males!S10+Females!S10</f>
+        <v>7499</v>
+      </c>
+      <c r="T10" s="2">
+        <f>Males!T10+Females!T10</f>
+        <v>7641</v>
+      </c>
+      <c r="U10" s="2">
+        <f>Males!U10+Females!U10</f>
+        <v>7664</v>
+      </c>
+      <c r="V10" s="2">
+        <f>Males!V10+Females!V10</f>
+        <v>7470</v>
+      </c>
+      <c r="W10" s="2">
+        <f>Males!W10+Females!W10</f>
+        <v>7093</v>
+      </c>
+      <c r="X10" s="2">
+        <f>Males!X10+Females!X10</f>
+        <v>6660</v>
+      </c>
+      <c r="Y10" s="2">
+        <f>Males!Y10+Females!Y10</f>
+        <v>6270</v>
+      </c>
+      <c r="Z10" s="2">
+        <f>Males!Z10+Females!Z10</f>
+        <v>5985</v>
+      </c>
+      <c r="AA10" s="2">
+        <f>Males!AA10+Females!AA10</f>
+        <v>5844</v>
+      </c>
+      <c r="AB10" s="2">
+        <f>Males!AB10+Females!AB10</f>
+        <v>5925</v>
+      </c>
+      <c r="AC10" s="2">
+        <f>Males!AC10+Females!AC10</f>
+        <v>6193</v>
+      </c>
+      <c r="AD10" s="2">
+        <f>Males!AD10+Females!AD10</f>
+        <v>6613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="str">
+        <f>Males!A11</f>
+        <v>40-44</v>
+      </c>
+      <c r="B11" s="2">
+        <f>Males!B11+Females!B11</f>
+        <v>4420</v>
+      </c>
+      <c r="C11" s="2">
+        <f>Males!C11+Females!C11</f>
+        <v>4540</v>
+      </c>
+      <c r="D11" s="2">
+        <f>Males!D11+Females!D11</f>
+        <v>4661</v>
+      </c>
+      <c r="E11" s="2">
+        <f>Males!E11+Females!E11</f>
+        <v>4739</v>
+      </c>
+      <c r="F11" s="2">
+        <f>Males!F11+Females!F11</f>
+        <v>4780</v>
+      </c>
+      <c r="G11" s="2">
+        <f>Males!G11+Females!G11</f>
+        <v>4776</v>
+      </c>
+      <c r="H11" s="2">
+        <f>Males!H11+Females!H11</f>
+        <v>4756</v>
+      </c>
+      <c r="I11" s="2">
+        <f>Males!I11+Females!I11</f>
+        <v>4658</v>
+      </c>
+      <c r="J11" s="2">
+        <f>Males!J11+Females!J11</f>
+        <v>4705</v>
+      </c>
+      <c r="K11" s="2">
+        <f>Males!K11+Females!K11</f>
+        <v>4820</v>
+      </c>
+      <c r="L11" s="2">
+        <f>Males!L11+Females!L11</f>
+        <v>4986</v>
+      </c>
+      <c r="M11" s="2">
+        <f>Males!M11+Females!M11</f>
+        <v>5187</v>
+      </c>
+      <c r="N11" s="2">
+        <f>Males!N11+Females!N11</f>
+        <v>5418</v>
+      </c>
+      <c r="O11" s="2">
+        <f>Males!O11+Females!O11</f>
+        <v>5680</v>
+      </c>
+      <c r="P11" s="2">
+        <f>Males!P11+Females!P11</f>
+        <v>5962</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>Males!Q11+Females!Q11</f>
+        <v>6022</v>
+      </c>
+      <c r="R11" s="2">
+        <f>Males!R11+Females!R11</f>
+        <v>6174</v>
+      </c>
+      <c r="S11" s="2">
+        <f>Males!S11+Females!S11</f>
+        <v>6297</v>
+      </c>
+      <c r="T11" s="2">
+        <f>Males!T11+Females!T11</f>
+        <v>6435</v>
+      </c>
+      <c r="U11" s="2">
+        <f>Males!U11+Females!U11</f>
+        <v>6612</v>
+      </c>
+      <c r="V11" s="2">
+        <f>Males!V11+Females!V11</f>
+        <v>6825</v>
+      </c>
+      <c r="W11" s="2">
+        <f>Males!W11+Females!W11</f>
+        <v>7047</v>
+      </c>
+      <c r="X11" s="2">
+        <f>Males!X11+Females!X11</f>
+        <v>7253</v>
+      </c>
+      <c r="Y11" s="2">
+        <f>Males!Y11+Females!Y11</f>
+        <v>7413</v>
+      </c>
+      <c r="Z11" s="2">
+        <f>Males!Z11+Females!Z11</f>
+        <v>7460</v>
+      </c>
+      <c r="AA11" s="2">
+        <f>Males!AA11+Females!AA11</f>
+        <v>7284</v>
+      </c>
+      <c r="AB11" s="2">
+        <f>Males!AB11+Females!AB11</f>
+        <v>6918</v>
+      </c>
+      <c r="AC11" s="2">
+        <f>Males!AC11+Females!AC11</f>
+        <v>6490</v>
+      </c>
+      <c r="AD11" s="2">
+        <f>Males!AD11+Females!AD11</f>
+        <v>6112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="str">
+        <f>Males!A12</f>
+        <v>45-49</v>
+      </c>
+      <c r="B12" s="2">
+        <f>Males!B12+Females!B12</f>
+        <v>3811</v>
+      </c>
+      <c r="C12" s="2">
+        <f>Males!C12+Females!C12</f>
+        <v>3855</v>
+      </c>
+      <c r="D12" s="2">
+        <f>Males!D12+Females!D12</f>
+        <v>3911</v>
+      </c>
+      <c r="E12" s="2">
+        <f>Males!E12+Females!E12</f>
+        <v>3985</v>
+      </c>
+      <c r="F12" s="2">
+        <f>Males!F12+Females!F12</f>
+        <v>4078</v>
+      </c>
+      <c r="G12" s="2">
+        <f>Males!G12+Females!G12</f>
+        <v>4162</v>
+      </c>
+      <c r="H12" s="2">
+        <f>Males!H12+Females!H12</f>
+        <v>4234</v>
+      </c>
+      <c r="I12" s="2">
+        <f>Males!I12+Females!I12</f>
+        <v>4196</v>
+      </c>
+      <c r="J12" s="2">
+        <f>Males!J12+Females!J12</f>
+        <v>4221</v>
+      </c>
+      <c r="K12" s="2">
+        <f>Males!K12+Females!K12</f>
+        <v>4233</v>
+      </c>
+      <c r="L12" s="2">
+        <f>Males!L12+Females!L12</f>
+        <v>4241</v>
+      </c>
+      <c r="M12" s="2">
+        <f>Males!M12+Females!M12</f>
+        <v>4255</v>
+      </c>
+      <c r="N12" s="2">
+        <f>Males!N12+Females!N12</f>
+        <v>4304</v>
+      </c>
+      <c r="O12" s="2">
+        <f>Males!O12+Females!O12</f>
+        <v>4404</v>
+      </c>
+      <c r="P12" s="2">
+        <f>Males!P12+Females!P12</f>
+        <v>4534</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>Males!Q12+Females!Q12</f>
+        <v>4759</v>
+      </c>
+      <c r="R12" s="2">
+        <f>Males!R12+Females!R12</f>
+        <v>4905</v>
+      </c>
+      <c r="S12" s="2">
+        <f>Males!S12+Females!S12</f>
+        <v>5076</v>
+      </c>
+      <c r="T12" s="2">
+        <f>Males!T12+Females!T12</f>
+        <v>5305</v>
+      </c>
+      <c r="U12" s="2">
+        <f>Males!U12+Females!U12</f>
+        <v>5513</v>
+      </c>
+      <c r="V12" s="2">
+        <f>Males!V12+Females!V12</f>
+        <v>5687</v>
+      </c>
+      <c r="W12" s="2">
+        <f>Males!W12+Females!W12</f>
+        <v>5872</v>
+      </c>
+      <c r="X12" s="2">
+        <f>Males!X12+Females!X12</f>
+        <v>6047</v>
+      </c>
+      <c r="Y12" s="2">
+        <f>Males!Y12+Females!Y12</f>
+        <v>6201</v>
+      </c>
+      <c r="Z12" s="2">
+        <f>Males!Z12+Females!Z12</f>
+        <v>6389</v>
+      </c>
+      <c r="AA12" s="2">
+        <f>Males!AA12+Females!AA12</f>
+        <v>6610</v>
+      </c>
+      <c r="AB12" s="2">
+        <f>Males!AB12+Females!AB12</f>
+        <v>6833</v>
+      </c>
+      <c r="AC12" s="2">
+        <f>Males!AC12+Females!AC12</f>
+        <v>7035</v>
+      </c>
+      <c r="AD12" s="2">
+        <f>Males!AD12+Females!AD12</f>
+        <v>7201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="str">
+        <f>Males!A13</f>
+        <v>50-54</v>
+      </c>
+      <c r="B13" s="2">
+        <f>Males!B13+Females!B13</f>
+        <v>3235</v>
+      </c>
+      <c r="C13" s="2">
+        <f>Males!C13+Females!C13</f>
+        <v>3293</v>
+      </c>
+      <c r="D13" s="2">
+        <f>Males!D13+Females!D13</f>
+        <v>3367</v>
+      </c>
+      <c r="E13" s="2">
+        <f>Males!E13+Females!E13</f>
+        <v>3449</v>
+      </c>
+      <c r="F13" s="2">
+        <f>Males!F13+Females!F13</f>
+        <v>3522</v>
+      </c>
+      <c r="G13" s="2">
+        <f>Males!G13+Females!G13</f>
+        <v>3571</v>
+      </c>
+      <c r="H13" s="2">
+        <f>Males!H13+Females!H13</f>
+        <v>3610</v>
+      </c>
+      <c r="I13" s="2">
+        <f>Males!I13+Females!I13</f>
+        <v>3577</v>
+      </c>
+      <c r="J13" s="2">
+        <f>Males!J13+Females!J13</f>
+        <v>3629</v>
+      </c>
+      <c r="K13" s="2">
+        <f>Males!K13+Females!K13</f>
+        <v>3689</v>
+      </c>
+      <c r="L13" s="2">
+        <f>Males!L13+Females!L13</f>
+        <v>3734</v>
+      </c>
+      <c r="M13" s="2">
+        <f>Males!M13+Females!M13</f>
+        <v>3744</v>
+      </c>
+      <c r="N13" s="2">
+        <f>Males!N13+Females!N13</f>
+        <v>3738</v>
+      </c>
+      <c r="O13" s="2">
+        <f>Males!O13+Females!O13</f>
+        <v>3762</v>
+      </c>
+      <c r="P13" s="2">
+        <f>Males!P13+Females!P13</f>
+        <v>3803</v>
+      </c>
+      <c r="Q13" s="2">
+        <f>Males!Q13+Females!Q13</f>
+        <v>3978</v>
+      </c>
+      <c r="R13" s="2">
+        <f>Males!R13+Females!R13</f>
+        <v>4053</v>
+      </c>
+      <c r="S13" s="2">
+        <f>Males!S13+Females!S13</f>
+        <v>4090</v>
+      </c>
+      <c r="T13" s="2">
+        <f>Males!T13+Females!T13</f>
+        <v>4160</v>
+      </c>
+      <c r="U13" s="2">
+        <f>Males!U13+Females!U13</f>
+        <v>4277</v>
+      </c>
+      <c r="V13" s="2">
+        <f>Males!V13+Females!V13</f>
+        <v>4427</v>
+      </c>
+      <c r="W13" s="2">
+        <f>Males!W13+Females!W13</f>
+        <v>4602</v>
+      </c>
+      <c r="X13" s="2">
+        <f>Males!X13+Females!X13</f>
+        <v>4817</v>
+      </c>
+      <c r="Y13" s="2">
+        <f>Males!Y13+Females!Y13</f>
+        <v>5055</v>
+      </c>
+      <c r="Z13" s="2">
+        <f>Males!Z13+Females!Z13</f>
+        <v>5270</v>
+      </c>
+      <c r="AA13" s="2">
+        <f>Males!AA13+Females!AA13</f>
+        <v>5448</v>
+      </c>
+      <c r="AB13" s="2">
+        <f>Males!AB13+Females!AB13</f>
+        <v>5631</v>
+      </c>
+      <c r="AC13" s="2">
+        <f>Males!AC13+Females!AC13</f>
+        <v>5800</v>
+      </c>
+      <c r="AD13" s="2">
+        <f>Males!AD13+Females!AD13</f>
+        <v>5955</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="str">
+        <f>Males!A14</f>
+        <v>55-59</v>
+      </c>
+      <c r="B14" s="2">
+        <f>Males!B14+Females!B14</f>
+        <v>2829</v>
+      </c>
+      <c r="C14" s="2">
+        <f>Males!C14+Females!C14</f>
+        <v>2840</v>
+      </c>
+      <c r="D14" s="2">
+        <f>Males!D14+Females!D14</f>
+        <v>2859</v>
+      </c>
+      <c r="E14" s="2">
+        <f>Males!E14+Females!E14</f>
+        <v>2890</v>
+      </c>
+      <c r="F14" s="2">
+        <f>Males!F14+Females!F14</f>
+        <v>2944</v>
+      </c>
+      <c r="G14" s="2">
+        <f>Males!G14+Females!G14</f>
+        <v>2994</v>
+      </c>
+      <c r="H14" s="2">
+        <f>Males!H14+Females!H14</f>
+        <v>3053</v>
+      </c>
+      <c r="I14" s="2">
+        <f>Males!I14+Females!I14</f>
+        <v>3043</v>
+      </c>
+      <c r="J14" s="2">
+        <f>Males!J14+Females!J14</f>
+        <v>3098</v>
+      </c>
+      <c r="K14" s="2">
+        <f>Males!K14+Females!K14</f>
+        <v>3154</v>
+      </c>
+      <c r="L14" s="2">
+        <f>Males!L14+Females!L14</f>
+        <v>3201</v>
+      </c>
+      <c r="M14" s="2">
+        <f>Males!M14+Females!M14</f>
+        <v>3233</v>
+      </c>
+      <c r="N14" s="2">
+        <f>Males!N14+Females!N14</f>
+        <v>3269</v>
+      </c>
+      <c r="O14" s="2">
+        <f>Males!O14+Females!O14</f>
+        <v>3298</v>
+      </c>
+      <c r="P14" s="2">
+        <f>Males!P14+Females!P14</f>
+        <v>3324</v>
+      </c>
+      <c r="Q14" s="2">
+        <f>Males!Q14+Females!Q14</f>
+        <v>3326</v>
+      </c>
+      <c r="R14" s="2">
+        <f>Males!R14+Females!R14</f>
+        <v>3353</v>
+      </c>
+      <c r="S14" s="2">
+        <f>Males!S14+Females!S14</f>
+        <v>3367</v>
+      </c>
+      <c r="T14" s="2">
+        <f>Males!T14+Females!T14</f>
+        <v>3423</v>
+      </c>
+      <c r="U14" s="2">
+        <f>Males!U14+Females!U14</f>
+        <v>3520</v>
+      </c>
+      <c r="V14" s="2">
+        <f>Males!V14+Females!V14</f>
+        <v>3635</v>
+      </c>
+      <c r="W14" s="2">
+        <f>Males!W14+Females!W14</f>
+        <v>3736</v>
+      </c>
+      <c r="X14" s="2">
+        <f>Males!X14+Females!X14</f>
+        <v>3813</v>
+      </c>
+      <c r="Y14" s="2">
+        <f>Males!Y14+Females!Y14</f>
+        <v>3891</v>
+      </c>
+      <c r="Z14" s="2">
+        <f>Males!Z14+Females!Z14</f>
+        <v>4010</v>
+      </c>
+      <c r="AA14" s="2">
+        <f>Males!AA14+Females!AA14</f>
+        <v>4161</v>
+      </c>
+      <c r="AB14" s="2">
+        <f>Males!AB14+Females!AB14</f>
+        <v>4335</v>
+      </c>
+      <c r="AC14" s="2">
+        <f>Males!AC14+Females!AC14</f>
+        <v>4541</v>
+      </c>
+      <c r="AD14" s="2">
+        <f>Males!AD14+Females!AD14</f>
+        <v>4777</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="str">
+        <f>Males!A15</f>
+        <v>60-64</v>
+      </c>
+      <c r="B15" s="2">
+        <f>Males!B15+Females!B15</f>
+        <v>2298</v>
+      </c>
+      <c r="C15" s="2">
+        <f>Males!C15+Females!C15</f>
+        <v>2340</v>
+      </c>
+      <c r="D15" s="2">
+        <f>Males!D15+Females!D15</f>
+        <v>2391</v>
+      </c>
+      <c r="E15" s="2">
+        <f>Males!E15+Females!E15</f>
+        <v>2417</v>
+      </c>
+      <c r="F15" s="2">
+        <f>Males!F15+Females!F15</f>
+        <v>2448</v>
+      </c>
+      <c r="G15" s="2">
+        <f>Males!G15+Females!G15</f>
+        <v>2463</v>
+      </c>
+      <c r="H15" s="2">
+        <f>Males!H15+Females!H15</f>
+        <v>2480</v>
+      </c>
+      <c r="I15" s="2">
+        <f>Males!I15+Females!I15</f>
+        <v>2459</v>
+      </c>
+      <c r="J15" s="2">
+        <f>Males!J15+Females!J15</f>
+        <v>2509</v>
+      </c>
+      <c r="K15" s="2">
+        <f>Males!K15+Females!K15</f>
+        <v>2580</v>
+      </c>
+      <c r="L15" s="2">
+        <f>Males!L15+Females!L15</f>
+        <v>2649</v>
+      </c>
+      <c r="M15" s="2">
+        <f>Males!M15+Females!M15</f>
+        <v>2696</v>
+      </c>
+      <c r="N15" s="2">
+        <f>Males!N15+Females!N15</f>
+        <v>2730</v>
+      </c>
+      <c r="O15" s="2">
+        <f>Males!O15+Females!O15</f>
+        <v>2746</v>
+      </c>
+      <c r="P15" s="2">
+        <f>Males!P15+Females!P15</f>
+        <v>2768</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>Males!Q15+Females!Q15</f>
+        <v>2663</v>
+      </c>
+      <c r="R15" s="2">
+        <f>Males!R15+Females!R15</f>
+        <v>2739</v>
+      </c>
+      <c r="S15" s="2">
+        <f>Males!S15+Females!S15</f>
+        <v>2788</v>
+      </c>
+      <c r="T15" s="2">
+        <f>Males!T15+Females!T15</f>
+        <v>2856</v>
+      </c>
+      <c r="U15" s="2">
+        <f>Males!U15+Females!U15</f>
+        <v>2907</v>
+      </c>
+      <c r="V15" s="2">
+        <f>Males!V15+Females!V15</f>
+        <v>2945</v>
+      </c>
+      <c r="W15" s="2">
+        <f>Males!W15+Females!W15</f>
+        <v>2993</v>
+      </c>
+      <c r="X15" s="2">
+        <f>Males!X15+Females!X15</f>
+        <v>3045</v>
+      </c>
+      <c r="Y15" s="2">
+        <f>Males!Y15+Females!Y15</f>
+        <v>3108</v>
+      </c>
+      <c r="Z15" s="2">
+        <f>Males!Z15+Females!Z15</f>
+        <v>3206</v>
+      </c>
+      <c r="AA15" s="2">
+        <f>Males!AA15+Females!AA15</f>
+        <v>3325</v>
+      </c>
+      <c r="AB15" s="2">
+        <f>Males!AB15+Females!AB15</f>
+        <v>3427</v>
+      </c>
+      <c r="AC15" s="2">
+        <f>Males!AC15+Females!AC15</f>
+        <v>3496</v>
+      </c>
+      <c r="AD15" s="2">
+        <f>Males!AD15+Females!AD15</f>
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1" t="str">
+        <f>Males!A16</f>
+        <v>65-69</v>
+      </c>
+      <c r="B16" s="2">
+        <f>Males!B16+Females!B16</f>
+        <v>1706</v>
+      </c>
+      <c r="C16" s="2">
+        <f>Males!C16+Females!C16</f>
+        <v>1740</v>
+      </c>
+      <c r="D16" s="2">
+        <f>Males!D16+Females!D16</f>
+        <v>1783</v>
+      </c>
+      <c r="E16" s="2">
+        <f>Males!E16+Females!E16</f>
+        <v>1804</v>
+      </c>
+      <c r="F16" s="2">
+        <f>Males!F16+Females!F16</f>
+        <v>1833</v>
+      </c>
+      <c r="G16" s="2">
+        <f>Males!G16+Females!G16</f>
+        <v>1842</v>
+      </c>
+      <c r="H16" s="2">
+        <f>Males!H16+Females!H16</f>
+        <v>1844</v>
+      </c>
+      <c r="I16" s="2">
+        <f>Males!I16+Females!I16</f>
+        <v>1814</v>
+      </c>
+      <c r="J16" s="2">
+        <f>Males!J16+Females!J16</f>
+        <v>1832</v>
+      </c>
+      <c r="K16" s="2">
+        <f>Males!K16+Females!K16</f>
+        <v>1866</v>
+      </c>
+      <c r="L16" s="2">
+        <f>Males!L16+Females!L16</f>
+        <v>1917</v>
+      </c>
+      <c r="M16" s="2">
+        <f>Males!M16+Females!M16</f>
+        <v>1972</v>
+      </c>
+      <c r="N16" s="2">
+        <f>Males!N16+Females!N16</f>
+        <v>2040</v>
+      </c>
+      <c r="O16" s="2">
+        <f>Males!O16+Females!O16</f>
+        <v>2103</v>
+      </c>
+      <c r="P16" s="2">
+        <f>Males!P16+Females!P16</f>
+        <v>2157</v>
+      </c>
+      <c r="Q16" s="2">
+        <f>Males!Q16+Females!Q16</f>
+        <v>1835</v>
+      </c>
+      <c r="R16" s="2">
+        <f>Males!R16+Females!R16</f>
+        <v>1908</v>
+      </c>
+      <c r="S16" s="2">
+        <f>Males!S16+Females!S16</f>
+        <v>1968</v>
+      </c>
+      <c r="T16" s="2">
+        <f>Males!T16+Females!T16</f>
+        <v>2061</v>
+      </c>
+      <c r="U16" s="2">
+        <f>Males!U16+Females!U16</f>
+        <v>2160</v>
+      </c>
+      <c r="V16" s="2">
+        <f>Males!V16+Females!V16</f>
+        <v>2251</v>
+      </c>
+      <c r="W16" s="2">
+        <f>Males!W16+Females!W16</f>
+        <v>2335</v>
+      </c>
+      <c r="X16" s="2">
+        <f>Males!X16+Females!X16</f>
+        <v>2416</v>
+      </c>
+      <c r="Y16" s="2">
+        <f>Males!Y16+Females!Y16</f>
+        <v>2485</v>
+      </c>
+      <c r="Z16" s="2">
+        <f>Males!Z16+Females!Z16</f>
+        <v>2533</v>
+      </c>
+      <c r="AA16" s="2">
+        <f>Males!AA16+Females!AA16</f>
+        <v>2572</v>
+      </c>
+      <c r="AB16" s="2">
+        <f>Males!AB16+Females!AB16</f>
+        <v>2623</v>
+      </c>
+      <c r="AC16" s="2">
+        <f>Males!AC16+Females!AC16</f>
+        <v>2672</v>
+      </c>
+      <c r="AD16" s="2">
+        <f>Males!AD16+Females!AD16</f>
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="str">
+        <f>Males!A17</f>
+        <v>70-74</v>
+      </c>
+      <c r="B17" s="2">
+        <f>Males!B17+Females!B17</f>
+        <v>1031</v>
+      </c>
+      <c r="C17" s="2">
+        <f>Males!C17+Females!C17</f>
+        <v>1084</v>
+      </c>
+      <c r="D17" s="2">
+        <f>Males!D17+Females!D17</f>
+        <v>1148</v>
+      </c>
+      <c r="E17" s="2">
+        <f>Males!E17+Females!E17</f>
+        <v>1191</v>
+      </c>
+      <c r="F17" s="2">
+        <f>Males!F17+Females!F17</f>
+        <v>1232</v>
+      </c>
+      <c r="G17" s="2">
+        <f>Males!G17+Females!G17</f>
+        <v>1241</v>
+      </c>
+      <c r="H17" s="2">
+        <f>Males!H17+Females!H17</f>
+        <v>1233</v>
+      </c>
+      <c r="I17" s="2">
+        <f>Males!I17+Females!I17</f>
+        <v>1205</v>
+      </c>
+      <c r="J17" s="2">
+        <f>Males!J17+Females!J17</f>
+        <v>1207</v>
+      </c>
+      <c r="K17" s="2">
+        <f>Males!K17+Females!K17</f>
+        <v>1212</v>
+      </c>
+      <c r="L17" s="2">
+        <f>Males!L17+Females!L17</f>
+        <v>1217</v>
+      </c>
+      <c r="M17" s="2">
+        <f>Males!M17+Females!M17</f>
+        <v>1216</v>
+      </c>
+      <c r="N17" s="2">
+        <f>Males!N17+Females!N17</f>
+        <v>1229</v>
+      </c>
+      <c r="O17" s="2">
+        <f>Males!O17+Females!O17</f>
+        <v>1272</v>
+      </c>
+      <c r="P17" s="2">
+        <f>Males!P17+Females!P17</f>
+        <v>1327</v>
+      </c>
+      <c r="Q17" s="2">
+        <f>Males!Q17+Females!Q17</f>
+        <v>1203</v>
+      </c>
+      <c r="R17" s="2">
+        <f>Males!R17+Females!R17</f>
+        <v>1232</v>
+      </c>
+      <c r="S17" s="2">
+        <f>Males!S17+Females!S17</f>
+        <v>1246</v>
+      </c>
+      <c r="T17" s="2">
+        <f>Males!T17+Females!T17</f>
+        <v>1294</v>
+      </c>
+      <c r="U17" s="2">
+        <f>Males!U17+Females!U17</f>
+        <v>1357</v>
+      </c>
+      <c r="V17" s="2">
+        <f>Males!V17+Females!V17</f>
+        <v>1423</v>
+      </c>
+      <c r="W17" s="2">
+        <f>Males!W17+Females!W17</f>
+        <v>1499</v>
+      </c>
+      <c r="X17" s="2">
+        <f>Males!X17+Females!X17</f>
+        <v>1581</v>
+      </c>
+      <c r="Y17" s="2">
+        <f>Males!Y17+Females!Y17</f>
+        <v>1665</v>
+      </c>
+      <c r="Z17" s="2">
+        <f>Males!Z17+Females!Z17</f>
+        <v>1750</v>
+      </c>
+      <c r="AA17" s="2">
+        <f>Males!AA17+Females!AA17</f>
+        <v>1835</v>
+      </c>
+      <c r="AB17" s="2">
+        <f>Males!AB17+Females!AB17</f>
+        <v>1913</v>
+      </c>
+      <c r="AC17" s="2">
+        <f>Males!AC17+Females!AC17</f>
+        <v>1981</v>
+      </c>
+      <c r="AD17" s="2">
+        <f>Males!AD17+Females!AD17</f>
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="str">
+        <f>Males!A18</f>
+        <v>75-79</v>
+      </c>
+      <c r="B18" s="2">
+        <f>Males!B18+Females!B18</f>
+        <v>563</v>
+      </c>
+      <c r="C18" s="2">
+        <f>Males!C18+Females!C18</f>
+        <v>571</v>
+      </c>
+      <c r="D18" s="2">
+        <f>Males!D18+Females!D18</f>
+        <v>592</v>
+      </c>
+      <c r="E18" s="2">
+        <f>Males!E18+Females!E18</f>
+        <v>617</v>
+      </c>
+      <c r="F18" s="2">
+        <f>Males!F18+Females!F18</f>
+        <v>649</v>
+      </c>
+      <c r="G18" s="2">
+        <f>Males!G18+Females!G18</f>
+        <v>663</v>
+      </c>
+      <c r="H18" s="2">
+        <f>Males!H18+Females!H18</f>
+        <v>667</v>
+      </c>
+      <c r="I18" s="2">
+        <f>Males!I18+Females!I18</f>
+        <v>665</v>
+      </c>
+      <c r="J18" s="2">
+        <f>Males!J18+Females!J18</f>
+        <v>680</v>
+      </c>
+      <c r="K18" s="2">
+        <f>Males!K18+Females!K18</f>
+        <v>690</v>
+      </c>
+      <c r="L18" s="2">
+        <f>Males!L18+Females!L18</f>
+        <v>696</v>
+      </c>
+      <c r="M18" s="2">
+        <f>Males!M18+Females!M18</f>
+        <v>695</v>
+      </c>
+      <c r="N18" s="2">
+        <f>Males!N18+Females!N18</f>
+        <v>693</v>
+      </c>
+      <c r="O18" s="2">
+        <f>Males!O18+Females!O18</f>
+        <v>706</v>
+      </c>
+      <c r="P18" s="2">
+        <f>Males!P18+Females!P18</f>
+        <v>719</v>
+      </c>
+      <c r="Q18" s="2">
+        <f>Males!Q18+Females!Q18</f>
+        <v>653</v>
+      </c>
+      <c r="R18" s="2">
+        <f>Males!R18+Females!R18</f>
+        <v>693</v>
+      </c>
+      <c r="S18" s="2">
+        <f>Males!S18+Females!S18</f>
+        <v>716</v>
+      </c>
+      <c r="T18" s="2">
+        <f>Males!T18+Females!T18</f>
+        <v>754</v>
+      </c>
+      <c r="U18" s="2">
+        <f>Males!U18+Females!U18</f>
+        <v>793</v>
+      </c>
+      <c r="V18" s="2">
+        <f>Males!V18+Females!V18</f>
+        <v>825</v>
+      </c>
+      <c r="W18" s="2">
+        <f>Males!W18+Females!W18</f>
+        <v>856</v>
+      </c>
+      <c r="X18" s="2">
+        <f>Males!X18+Females!X18</f>
+        <v>887</v>
+      </c>
+      <c r="Y18" s="2">
+        <f>Males!Y18+Females!Y18</f>
+        <v>926</v>
+      </c>
+      <c r="Z18" s="2">
+        <f>Males!Z18+Females!Z18</f>
+        <v>970</v>
+      </c>
+      <c r="AA18" s="2">
+        <f>Males!AA18+Females!AA18</f>
+        <v>1024</v>
+      </c>
+      <c r="AB18" s="2">
+        <f>Males!AB18+Females!AB18</f>
+        <v>1090</v>
+      </c>
+      <c r="AC18" s="2">
+        <f>Males!AC18+Females!AC18</f>
+        <v>1158</v>
+      </c>
+      <c r="AD18" s="2">
+        <f>Males!AD18+Females!AD18</f>
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1" t="str">
+        <f>Males!A19</f>
+        <v>80-84</v>
+      </c>
+      <c r="B19" s="2">
+        <f>Males!B19+Females!B19</f>
+        <v>288</v>
+      </c>
+      <c r="C19" s="2">
+        <f>Males!C19+Females!C19</f>
+        <v>300</v>
+      </c>
+      <c r="D19" s="2">
+        <f>Males!D19+Females!D19</f>
+        <v>314</v>
+      </c>
+      <c r="E19" s="2">
+        <f>Males!E19+Females!E19</f>
+        <v>322</v>
+      </c>
+      <c r="F19" s="2">
+        <f>Males!F19+Females!F19</f>
+        <v>329</v>
+      </c>
+      <c r="G19" s="2">
+        <f>Males!G19+Females!G19</f>
+        <v>322</v>
+      </c>
+      <c r="H19" s="2">
+        <f>Males!H19+Females!H19</f>
+        <v>310</v>
+      </c>
+      <c r="I19" s="2">
+        <f>Males!I19+Females!I19</f>
+        <v>301</v>
+      </c>
+      <c r="J19" s="2">
+        <f>Males!J19+Females!J19</f>
+        <v>307</v>
+      </c>
+      <c r="K19" s="2">
+        <f>Males!K19+Females!K19</f>
+        <v>315</v>
+      </c>
+      <c r="L19" s="2">
+        <f>Males!L19+Females!L19</f>
+        <v>318</v>
+      </c>
+      <c r="M19" s="2">
+        <f>Males!M19+Females!M19</f>
+        <v>316</v>
+      </c>
+      <c r="N19" s="2">
+        <f>Males!N19+Females!N19</f>
+        <v>317</v>
+      </c>
+      <c r="O19" s="2">
+        <f>Males!O19+Females!O19</f>
+        <v>323</v>
+      </c>
+      <c r="P19" s="2">
+        <f>Males!P19+Females!P19</f>
+        <v>330</v>
+      </c>
+      <c r="Q19" s="2">
+        <f>Males!Q19+Females!Q19</f>
+        <v>292</v>
+      </c>
+      <c r="R19" s="2">
+        <f>Males!R19+Females!R19</f>
+        <v>302</v>
+      </c>
+      <c r="S19" s="2">
+        <f>Males!S19+Females!S19</f>
+        <v>304</v>
+      </c>
+      <c r="T19" s="2">
+        <f>Males!T19+Females!T19</f>
+        <v>325</v>
+      </c>
+      <c r="U19" s="2">
+        <f>Males!U19+Females!U19</f>
+        <v>356</v>
+      </c>
+      <c r="V19" s="2">
+        <f>Males!V19+Females!V19</f>
+        <v>389</v>
+      </c>
+      <c r="W19" s="2">
+        <f>Males!W19+Females!W19</f>
+        <v>422</v>
+      </c>
+      <c r="X19" s="2">
+        <f>Males!X19+Females!X19</f>
+        <v>452</v>
+      </c>
+      <c r="Y19" s="2">
+        <f>Males!Y19+Females!Y19</f>
+        <v>477</v>
+      </c>
+      <c r="Z19" s="2">
+        <f>Males!Z19+Females!Z19</f>
+        <v>495</v>
+      </c>
+      <c r="AA19" s="2">
+        <f>Males!AA19+Females!AA19</f>
+        <v>515</v>
+      </c>
+      <c r="AB19" s="2">
+        <f>Males!AB19+Females!AB19</f>
+        <v>532</v>
+      </c>
+      <c r="AC19" s="2">
+        <f>Males!AC19+Females!AC19</f>
+        <v>550</v>
+      </c>
+      <c r="AD19" s="2">
+        <f>Males!AD19+Females!AD19</f>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="str">
+        <f>Males!A20</f>
+        <v>85 и старше</v>
+      </c>
+      <c r="B20" s="2">
+        <f>Males!B20+Females!B20</f>
+        <v>210</v>
+      </c>
+      <c r="C20" s="2">
+        <f>Males!C20+Females!C20</f>
+        <v>210</v>
+      </c>
+      <c r="D20" s="2">
+        <f>Males!D20+Females!D20</f>
+        <v>219</v>
+      </c>
+      <c r="E20" s="2">
+        <f>Males!E20+Females!E20</f>
+        <v>233</v>
+      </c>
+      <c r="F20" s="2">
+        <f>Males!F20+Females!F20</f>
+        <v>248</v>
+      </c>
+      <c r="G20" s="2">
+        <f>Males!G20+Females!G20</f>
+        <v>251</v>
+      </c>
+      <c r="H20" s="2">
+        <f>Males!H20+Females!H20</f>
+        <v>248</v>
+      </c>
+      <c r="I20" s="2">
+        <f>Males!I20+Females!I20</f>
+        <v>239</v>
+      </c>
+      <c r="J20" s="2">
+        <f>Males!J20+Females!J20</f>
+        <v>229</v>
+      </c>
+      <c r="K20" s="2">
+        <f>Males!K20+Females!K20</f>
+        <v>226</v>
+      </c>
+      <c r="L20" s="2">
+        <f>Males!L20+Females!L20</f>
+        <v>222</v>
+      </c>
+      <c r="M20" s="2">
+        <f>Males!M20+Females!M20</f>
+        <v>216</v>
+      </c>
+      <c r="N20" s="2">
+        <f>Males!N20+Females!N20</f>
+        <v>210</v>
+      </c>
+      <c r="O20" s="2">
+        <f>Males!O20+Females!O20</f>
+        <v>203</v>
+      </c>
+      <c r="P20" s="2">
+        <f>Males!P20+Females!P20</f>
+        <v>194</v>
+      </c>
+      <c r="Q20" s="2">
+        <f>Males!Q20+Females!Q20</f>
+        <v>190</v>
+      </c>
+      <c r="R20" s="2">
+        <f>Males!R20+Females!R20</f>
+        <v>197</v>
+      </c>
+      <c r="S20" s="2">
+        <f>Males!S20+Females!S20</f>
+        <v>195</v>
+      </c>
+      <c r="T20" s="2">
+        <f>Males!T20+Females!T20</f>
+        <v>205</v>
+      </c>
+      <c r="U20" s="2">
+        <f>Males!U20+Females!U20</f>
+        <v>218</v>
+      </c>
+      <c r="V20" s="2">
+        <f>Males!V20+Females!V20</f>
+        <v>229</v>
+      </c>
+      <c r="W20" s="2">
+        <f>Males!W20+Females!W20</f>
+        <v>241</v>
+      </c>
+      <c r="X20" s="2">
+        <f>Males!X20+Females!X20</f>
+        <v>253</v>
+      </c>
+      <c r="Y20" s="2">
+        <f>Males!Y20+Females!Y20</f>
+        <v>267</v>
+      </c>
+      <c r="Z20" s="2">
+        <f>Males!Z20+Females!Z20</f>
+        <v>283</v>
+      </c>
+      <c r="AA20" s="2">
+        <f>Males!AA20+Females!AA20</f>
+        <v>301</v>
+      </c>
+      <c r="AB20" s="2">
+        <f>Males!AB20+Females!AB20</f>
+        <v>321</v>
+      </c>
+      <c r="AC20" s="2">
+        <f>Males!AC20+Females!AC20</f>
+        <v>338</v>
+      </c>
+      <c r="AD20" s="2">
+        <f>Males!AD20+Females!AD20</f>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2">
+        <f>SUM(B3:B20)-B2</f>
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" ref="C22:AD22" si="0">SUM(C3:C20)-C2</f>
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O22" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="R22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="T22" s="2">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="U22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="V22" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="X22" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y22" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z22" s="2">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="AA22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="AB22" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="AD22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>